--- a/research/traditional_assets/database/data/denmark/denmark_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_oil_gas_production_and_exploration.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>0.788</v>
+        <v>-1.23</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,64 +606,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="V2">
-        <v>0.003243243243243243</v>
+        <v>0.004026845637583893</v>
       </c>
       <c r="W2">
-        <v>-0.05288590604026846</v>
+        <v>0.1025</v>
       </c>
       <c r="X2">
-        <v>0.3340333319957807</v>
+        <v>0.47215027843338</v>
       </c>
       <c r="Y2">
-        <v>-0.3869192380360492</v>
+        <v>-0.3696502784333801</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>-0.10271546635183</v>
       </c>
       <c r="AB2">
-        <v>0.1221895355175073</v>
+        <v>0.08208104597406973</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1847965123258997</v>
       </c>
       <c r="AD2">
-        <v>15.4</v>
+        <v>16.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.4</v>
+        <v>16.8</v>
       </c>
       <c r="AG2">
-        <v>15.388</v>
+        <v>16.794</v>
       </c>
       <c r="AH2">
-        <v>0.806282722513089</v>
+        <v>0.9185347184253692</v>
       </c>
       <c r="AI2">
-        <v>4.529411764705882</v>
+        <v>5.999999999999999</v>
       </c>
       <c r="AJ2">
-        <v>0.8061609388097234</v>
+        <v>0.9185079851236054</v>
       </c>
       <c r="AK2">
-        <v>4.541912632821724</v>
+        <v>6.01073729420186</v>
       </c>
       <c r="AL2">
-        <v>1.93</v>
+        <v>0.458</v>
       </c>
       <c r="AM2">
-        <v>1.93</v>
+        <v>0.458</v>
       </c>
       <c r="AO2">
-        <v>-0.1300518134715026</v>
+        <v>-0.7598253275109169</v>
       </c>
       <c r="AQ2">
-        <v>-0.1300518134715026</v>
+        <v>-0.7598253275109169</v>
       </c>
     </row>
     <row r="3">
@@ -683,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>0.788</v>
+        <v>-1.23</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -692,7 +701,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -701,64 +710,73 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="V3">
-        <v>0.003243243243243243</v>
+        <v>0.004026845637583893</v>
       </c>
       <c r="W3">
-        <v>-0.05288590604026846</v>
+        <v>0.1025</v>
       </c>
       <c r="X3">
-        <v>0.3340333319957807</v>
+        <v>0.47215027843338</v>
       </c>
       <c r="Y3">
-        <v>-0.3869192380360492</v>
+        <v>-0.3696502784333801</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-0.10271546635183</v>
       </c>
       <c r="AB3">
-        <v>0.1221895355175073</v>
+        <v>0.08208104597406973</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1847965123258997</v>
       </c>
       <c r="AD3">
-        <v>15.4</v>
+        <v>16.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.4</v>
+        <v>16.8</v>
       </c>
       <c r="AG3">
-        <v>15.388</v>
+        <v>16.794</v>
       </c>
       <c r="AH3">
-        <v>0.806282722513089</v>
+        <v>0.9185347184253692</v>
       </c>
       <c r="AI3">
-        <v>4.529411764705882</v>
+        <v>5.999999999999999</v>
       </c>
       <c r="AJ3">
-        <v>0.8061609388097234</v>
+        <v>0.9185079851236054</v>
       </c>
       <c r="AK3">
-        <v>4.541912632821724</v>
+        <v>6.01073729420186</v>
       </c>
       <c r="AL3">
-        <v>1.93</v>
+        <v>0.458</v>
       </c>
       <c r="AM3">
-        <v>1.93</v>
+        <v>0.458</v>
       </c>
       <c r="AO3">
-        <v>-0.1300518134715026</v>
+        <v>-0.7598253275109169</v>
       </c>
       <c r="AQ3">
-        <v>-0.1300518134715026</v>
+        <v>-0.7598253275109169</v>
       </c>
     </row>
   </sheetData>
